--- a/datos/Semana36.xlsx
+++ b/datos/Semana36.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="26">
   <si>
     <t>Fecha</t>
   </si>
@@ -39,9 +39,6 @@
     <t>Turno</t>
   </si>
   <si>
-    <t>31-ago</t>
-  </si>
-  <si>
     <t>HABILITAR ESTANQUE</t>
   </si>
   <si>
@@ -75,15 +72,9 @@
     <t>MP HIDROLAVADORA POWER WASH GRIS</t>
   </si>
   <si>
-    <t>01-sept</t>
-  </si>
-  <si>
     <t>LIMPIEZA MOTOR MOLEDORA ENSILAJE 6M</t>
   </si>
   <si>
-    <t>02-sept</t>
-  </si>
-  <si>
     <t>CAMBIO ACEITE COMPRESOR RILES</t>
   </si>
   <si>
@@ -93,16 +84,10 @@
     <t>RBM</t>
   </si>
   <si>
-    <t>03-ago</t>
-  </si>
-  <si>
     <t>INSTALACIÓN FOTOPERIODO TK 1 (PRE-SMOLT)</t>
   </si>
   <si>
     <t>MP MEDICIÓN AISLACIÓN Y RESISTENCIA 1A</t>
-  </si>
-  <si>
-    <t>04-ago</t>
   </si>
   <si>
     <t>MP LUBRICACION EJE Y RUEDAS FTR EFLUE</t>
@@ -155,7 +140,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -164,6 +149,9 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -423,8 +411,8 @@
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="3" t="s">
-        <v>6</v>
+      <c r="A2" s="4">
+        <v>46265</v>
       </c>
       <c r="B2" s="3">
         <v>10035268</v>
@@ -433,18 +421,18 @@
         <v>10013917</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F2" s="3" t="s">
-        <v>9</v>
-      </c>
     </row>
     <row r="3" spans="1:6">
-      <c r="A3" s="3" t="s">
-        <v>6</v>
+      <c r="A3" s="4">
+        <v>46265</v>
       </c>
       <c r="B3" s="3">
         <v>10034959</v>
@@ -453,18 +441,18 @@
         <v>20019455</v>
       </c>
       <c r="D3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="F3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="F3" s="3" t="s">
-        <v>12</v>
-      </c>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="3" t="s">
-        <v>6</v>
+      <c r="A4" s="4">
+        <v>46265</v>
       </c>
       <c r="B4" s="3">
         <v>10034963</v>
@@ -473,16 +461,16 @@
         <v>20019458</v>
       </c>
       <c r="D4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="E4" s="2" t="s">
-        <v>14</v>
-      </c>
       <c r="F4" s="3"/>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="3" t="s">
-        <v>6</v>
+      <c r="A5" s="4">
+        <v>46265</v>
       </c>
       <c r="B5" s="3">
         <v>10034826</v>
@@ -491,16 +479,16 @@
         <v>20019776</v>
       </c>
       <c r="D5" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="E5" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="F5" s="3"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="3" t="s">
-        <v>6</v>
+      <c r="A6" s="4">
+        <v>46265</v>
       </c>
       <c r="B6" s="3">
         <v>10033692</v>
@@ -509,16 +497,16 @@
         <v>20018204</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F6" s="3"/>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
-        <v>18</v>
+      <c r="A7" s="4">
+        <v>46266</v>
       </c>
       <c r="B7" s="3">
         <v>10034951</v>
@@ -527,18 +515,18 @@
         <v>20018964</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="E7" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F7" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F7" s="3" t="s">
-        <v>9</v>
-      </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
-        <v>18</v>
+      <c r="A8" s="4">
+        <v>46266</v>
       </c>
       <c r="B8" s="3">
         <v>10034942</v>
@@ -547,18 +535,18 @@
         <v>20017773</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="3" t="s">
-        <v>20</v>
+      <c r="A9" s="4">
+        <v>46267</v>
       </c>
       <c r="B9" s="3">
         <v>10034950</v>
@@ -567,18 +555,18 @@
         <v>20018769</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="E9" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F9" s="3" t="s">
-        <v>9</v>
-      </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="3" t="s">
-        <v>20</v>
+      <c r="A10" s="4">
+        <v>46267</v>
       </c>
       <c r="B10" s="3">
         <v>10033902</v>
@@ -587,16 +575,16 @@
         <v>20018764</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F10" s="3"/>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="3" t="s">
-        <v>24</v>
+      <c r="A11" s="4">
+        <v>46268</v>
       </c>
       <c r="B11" s="3">
         <v>10034496</v>
@@ -605,18 +593,18 @@
         <v>20019494</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E11" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F11" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F11" s="3" t="s">
-        <v>9</v>
-      </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="3" t="s">
-        <v>24</v>
+      <c r="A12" s="4">
+        <v>46268</v>
       </c>
       <c r="B12" s="3">
         <v>10034952</v>
@@ -625,18 +613,18 @@
         <v>20018623</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="3" t="s">
-        <v>24</v>
+      <c r="A13" s="4">
+        <v>46268</v>
       </c>
       <c r="B13" s="3">
         <v>10034964</v>
@@ -645,18 +633,18 @@
         <v>20018961</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="3" t="s">
-        <v>27</v>
+      <c r="A14" s="4">
+        <v>46269</v>
       </c>
       <c r="B14" s="3">
         <v>10034504</v>
@@ -665,13 +653,13 @@
         <v>20019505</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="E14" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F14" s="3" t="s">
         <v>8</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>9</v>
       </c>
     </row>
   </sheetData>
